--- a/Processos/Processos-modelo.xlsx
+++ b/Processos/Processos-modelo.xlsx
@@ -21,7 +21,7 @@
     <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Area" vbProcedure="false">Checklist!$B$1:$E$24</definedName>
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">Elementos!$B$1:$N$48</definedName>
     <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Area" vbProcedure="false">'Exemplo 1 - Pizzaria'!$B$1:$Q$61</definedName>
-    <definedName function="false" hidden="false" localSheetId="7" name="_xlnm.Print_Area" vbProcedure="false">'Exemplo 2 - Compras'!$B$1:$H$56</definedName>
+    <definedName function="false" hidden="false" localSheetId="7" name="_xlnm.Print_Area" vbProcedure="false">'Exemplo 2 - Compras'!$B$1:$H$58</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Instruções!$B$1:$C$41</definedName>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">Interações!$B$1:$R$24</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Processos!$B$1:$K$29</definedName>
@@ -303,7 +303,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="344">
   <si>
     <t xml:space="preserve">Mapa de processos e tartaruga — Como usar esta planilha</t>
   </si>
@@ -1142,7 +1142,7 @@
     <t xml:space="preserve">Requisição aprovada, com especificação</t>
   </si>
   <si>
-    <t xml:space="preserve">Áreas requisitantes</t>
+    <t xml:space="preserve">Produção e Manutenção</t>
   </si>
   <si>
     <t xml:space="preserve">Plano de produção do mês</t>
@@ -1157,6 +1157,18 @@
     <t xml:space="preserve">Desenvolvimento de produto</t>
   </si>
   <si>
+    <t xml:space="preserve">Resultado da inspeção de recebimento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laboratório e controle da qualidade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resultados de auditoria e ações</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gestão do sistema da qualidade</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pedido de compra emitido</t>
   </si>
   <si>
@@ -1166,15 +1178,9 @@
     <t xml:space="preserve">Material recebido e conferido</t>
   </si>
   <si>
-    <t xml:space="preserve">Produção e Manutenção</t>
-  </si>
-  <si>
     <t xml:space="preserve">Avaliação dos fornecedores</t>
   </si>
   <si>
-    <t xml:space="preserve">Gestão do sistema da qualidade</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sistema de compras</t>
   </si>
   <si>
@@ -1286,22 +1292,19 @@
     <t xml:space="preserve">4 · Produção</t>
   </si>
   <si>
+    <t xml:space="preserve">Requisição de compra, com especificação, e plano de produção do mês</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 · Laboratório e controle da qualidade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 · Manutenção</t>
+  </si>
+  <si>
     <t xml:space="preserve">Requisição de compra, com especificação</t>
   </si>
   <si>
-    <t xml:space="preserve">5 · Laboratório e controle da qualidade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resultado da inspeção de recebimento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 · Manutenção</t>
-  </si>
-  <si>
     <t xml:space="preserve">9 · Gestão do sistema da qualidade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resultados de auditoria e ações</t>
   </si>
   <si>
     <t xml:space="preserve">Peças e serviços de manutenção</t>
@@ -2013,11 +2016,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="18913725"/>
-        <c:axId val="46382576"/>
+        <c:axId val="87258834"/>
+        <c:axId val="53690365"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="18913725"/>
+        <c:axId val="87258834"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2049,7 +2052,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="46382576"/>
+        <c:crossAx val="53690365"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2057,7 +2060,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="46382576"/>
+        <c:axId val="53690365"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -2098,7 +2101,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="18913725"/>
+        <c:crossAx val="87258834"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="0.25"/>
@@ -2232,7 +2235,7 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>0.5625</c:v>
+                  <c:v>0.625</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0.875</c:v>
@@ -2264,11 +2267,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="25126884"/>
-        <c:axId val="27837735"/>
+        <c:axId val="339729"/>
+        <c:axId val="40387945"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="25126884"/>
+        <c:axId val="339729"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2300,7 +2303,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="27837735"/>
+        <c:crossAx val="40387945"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2308,7 +2311,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="27837735"/>
+        <c:axId val="40387945"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -2349,7 +2352,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="25126884"/>
+        <c:crossAx val="339729"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="0.25"/>
@@ -4653,13 +4656,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
+    <dataValidation allowBlank="true" error="Digite um número inteiro de 1 a 12." errorStyle="stop" errorTitle="Número inválido" operator="between" prompt="Número do processo, como na aba Processos." promptTitle="Número" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D4" type="whole">
+      <formula1>1</formula1>
+      <formula2>12</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H4" type="date">
       <formula1>36526</formula1>
       <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Digite um número inteiro de 1 a 12." errorStyle="stop" errorTitle="Número inválido" operator="between" prompt="Número do processo, como na aba Processos." promptTitle="Número" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D4" type="whole">
-      <formula1>1</formula1>
-      <formula2>12</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
@@ -5976,18 +5979,18 @@
         <v>160</v>
       </c>
       <c r="N11" s="40" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O11" s="40" t="s">
         <v>160</v>
       </c>
       <c r="P11" s="34" t="n">
         <f aca="false">IF(COUNTA(H11:O11)=0,"",COUNTIF(H11:O11,"Sim")+0.5*COUNTIF(H11:O11,"Parcial"))</f>
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="Q11" s="35" t="n">
         <f aca="false">P11/8</f>
-        <v>0.5625</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6441,7 +6444,7 @@
       </c>
       <c r="N20" s="35" t="n">
         <f aca="false">(COUNTIF(N11:N19,"Sim")+0.5*COUNTIF(N11:N19,"Parcial"))/ROWS(N11:N19)</f>
-        <v>0.333333333333333</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="O20" s="35" t="n">
         <f aca="false">(COUNTIF(O11:O19,"Sim")+0.5*COUNTIF(O11:O19,"Parcial"))/ROWS(O11:O19)</f>
@@ -6450,7 +6453,7 @@
       <c r="P20" s="6"/>
       <c r="Q20" s="35" t="n">
         <f aca="false">AVERAGE(Q11:Q19)</f>
-        <v>0.631944444444444</v>
+        <v>0.638888888888889</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6522,7 +6525,7 @@
       <c r="D26" s="22"/>
       <c r="E26" s="35" t="n">
         <f aca="false">Q20</f>
-        <v>0.631944444444444</v>
+        <v>0.638888888888889</v>
       </c>
       <c r="F26" s="35"/>
       <c r="G26" s="35"/>
@@ -6548,7 +6551,7 @@
       <c r="D28" s="22"/>
       <c r="E28" s="23" t="str">
         <f aca="false">INDEX(H10:O10,MATCH(MIN(H20:O20),H20:O20,0))</f>
-        <v>g · Avaliação e mudanças</v>
+        <v>c · Critérios e indicadores</v>
       </c>
       <c r="F28" s="23"/>
       <c r="G28" s="23"/>
@@ -7186,7 +7189,7 @@
     <tabColor rgb="FF5B6B76"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:H56"/>
+  <dimension ref="B1:H58"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -7370,7 +7373,7 @@
     </row>
     <row r="16" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C16" s="10"/>
       <c r="D16" s="7" t="s">
@@ -7385,7 +7388,7 @@
     </row>
     <row r="17" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C17" s="10"/>
       <c r="D17" s="7" t="s">
@@ -7414,32 +7417,32 @@
       <c r="H18" s="7"/>
     </row>
     <row r="19" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="C19" s="12"/>
+      <c r="B19" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C19" s="10"/>
       <c r="D19" s="7" t="s">
         <v>290</v>
       </c>
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
       <c r="G19" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="H19" s="7"/>
+    </row>
+    <row r="20" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C20" s="10"/>
+      <c r="D20" s="7" t="s">
         <v>291</v>
-      </c>
-      <c r="H19" s="7"/>
-    </row>
-    <row r="20" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="C20" s="12"/>
-      <c r="D20" s="7" t="s">
-        <v>292</v>
       </c>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
       <c r="G20" s="7" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="H20" s="7"/>
     </row>
@@ -7449,42 +7452,42 @@
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="7" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
       <c r="G21" s="7" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="H21" s="7"/>
     </row>
     <row r="22" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="7" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
       <c r="G22" s="7" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="H22" s="7"/>
     </row>
     <row r="23" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="7" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
       <c r="G23" s="7" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="H23" s="7"/>
     </row>
@@ -7494,42 +7497,42 @@
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="7" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
       <c r="G24" s="7" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="H24" s="7"/>
     </row>
     <row r="25" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="12" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C25" s="12"/>
       <c r="D25" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
       <c r="G25" s="7" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="H25" s="7"/>
     </row>
     <row r="26" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="12" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="7" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
       <c r="G26" s="7" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="H26" s="7"/>
     </row>
@@ -7539,42 +7542,42 @@
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="7" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
       <c r="G27" s="7" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="H27" s="7"/>
     </row>
     <row r="28" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="7" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E28" s="7"/>
       <c r="F28" s="7"/>
       <c r="G28" s="7" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H28" s="7"/>
     </row>
     <row r="29" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C29" s="12"/>
       <c r="D29" s="7" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E29" s="7"/>
       <c r="F29" s="7"/>
       <c r="G29" s="7" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="H29" s="7"/>
     </row>
@@ -7584,12 +7587,12 @@
       </c>
       <c r="C30" s="12"/>
       <c r="D30" s="7" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
       <c r="G30" s="7" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H30" s="7"/>
     </row>
@@ -7599,42 +7602,42 @@
       </c>
       <c r="C31" s="12"/>
       <c r="D31" s="7" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
       <c r="G31" s="7" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="H31" s="7"/>
     </row>
     <row r="32" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="42" t="s">
-        <v>136</v>
-      </c>
-      <c r="C32" s="42"/>
+      <c r="B32" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="C32" s="12"/>
       <c r="D32" s="7" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
       <c r="G32" s="7" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="H32" s="7"/>
     </row>
     <row r="33" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="42" t="s">
-        <v>136</v>
-      </c>
-      <c r="C33" s="42"/>
+      <c r="B33" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="C33" s="12"/>
       <c r="D33" s="7" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
       <c r="G33" s="7" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H33" s="7"/>
     </row>
@@ -7644,70 +7647,70 @@
       </c>
       <c r="C34" s="42"/>
       <c r="D34" s="7" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E34" s="7"/>
       <c r="F34" s="7"/>
       <c r="G34" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="H34" s="7"/>
+    </row>
+    <row r="35" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B35" s="42" t="s">
+        <v>136</v>
+      </c>
+      <c r="C35" s="42"/>
+      <c r="D35" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="H34" s="7"/>
-    </row>
-    <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="30" t="s">
+      <c r="H35" s="7"/>
+    </row>
+    <row r="36" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B36" s="42" t="s">
+        <v>136</v>
+      </c>
+      <c r="C36" s="42"/>
+      <c r="D36" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="C36" s="30"/>
-      <c r="D36" s="30"/>
-      <c r="E36" s="30"/>
-      <c r="F36" s="30"/>
-      <c r="G36" s="30"/>
-      <c r="H36" s="30"/>
-    </row>
-    <row r="37" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="23" t="s">
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="C37" s="23"/>
-      <c r="D37" s="23" t="s">
+      <c r="H36" s="7"/>
+    </row>
+    <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="30" t="s">
+        <v>324</v>
+      </c>
+      <c r="C38" s="30"/>
+      <c r="D38" s="30"/>
+      <c r="E38" s="30"/>
+      <c r="F38" s="30"/>
+      <c r="G38" s="30"/>
+      <c r="H38" s="30"/>
+    </row>
+    <row r="39" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B39" s="23" t="s">
+        <v>325</v>
+      </c>
+      <c r="C39" s="23"/>
+      <c r="D39" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="E37" s="23"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="23" t="s">
-        <v>324</v>
-      </c>
-      <c r="H37" s="23"/>
-    </row>
-    <row r="38" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="C38" s="4"/>
-      <c r="D38" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="H38" s="7"/>
-    </row>
-    <row r="39" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="C39" s="4"/>
-      <c r="D39" s="7" t="s">
+      <c r="E39" s="23"/>
+      <c r="F39" s="23"/>
+      <c r="G39" s="23" t="s">
         <v>326</v>
       </c>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="H39" s="7"/>
+      <c r="H39" s="23"/>
     </row>
     <row r="40" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="4" t="s">
@@ -7715,12 +7718,12 @@
       </c>
       <c r="C40" s="4"/>
       <c r="D40" s="7" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
       <c r="G40" s="7" t="s">
-        <v>329</v>
+        <v>282</v>
       </c>
       <c r="H40" s="7"/>
     </row>
@@ -7730,12 +7733,12 @@
       </c>
       <c r="C41" s="4"/>
       <c r="D41" s="7" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
       <c r="G41" s="7" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H41" s="7"/>
     </row>
@@ -7745,42 +7748,42 @@
       </c>
       <c r="C42" s="4"/>
       <c r="D42" s="7" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E42" s="7"/>
       <c r="F42" s="7"/>
       <c r="G42" s="7" t="s">
-        <v>332</v>
+        <v>284</v>
       </c>
       <c r="H42" s="7"/>
     </row>
     <row r="43" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="43" t="s">
-        <v>106</v>
-      </c>
-      <c r="C43" s="43"/>
+      <c r="B43" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C43" s="4"/>
       <c r="D43" s="7" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="E43" s="7"/>
       <c r="F43" s="7"/>
       <c r="G43" s="7" t="s">
-        <v>286</v>
+        <v>332</v>
       </c>
       <c r="H43" s="7"/>
     </row>
     <row r="44" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="43" t="s">
-        <v>106</v>
-      </c>
-      <c r="C44" s="43"/>
+      <c r="B44" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C44" s="4"/>
       <c r="D44" s="7" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="E44" s="7"/>
       <c r="F44" s="7"/>
       <c r="G44" s="7" t="s">
-        <v>333</v>
+        <v>286</v>
       </c>
       <c r="H44" s="7"/>
     </row>
@@ -7790,136 +7793,166 @@
       </c>
       <c r="C45" s="43"/>
       <c r="D45" s="7" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="E45" s="7"/>
       <c r="F45" s="7"/>
       <c r="G45" s="7" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="H45" s="7"/>
     </row>
-    <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="21" t="s">
+    <row r="46" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B46" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="C46" s="43"/>
+      <c r="D46" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="E46" s="7"/>
+      <c r="F46" s="7"/>
+      <c r="G46" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="H46" s="7"/>
+    </row>
+    <row r="47" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B47" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="C47" s="43"/>
+      <c r="D47" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="E47" s="7"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="H47" s="7"/>
+    </row>
+    <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B49" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="C47" s="21"/>
-      <c r="D47" s="21"/>
-      <c r="E47" s="21"/>
-      <c r="F47" s="21"/>
-      <c r="G47" s="21"/>
-      <c r="H47" s="21"/>
-    </row>
-    <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B48" s="22" t="s">
-        <v>334</v>
-      </c>
-      <c r="C48" s="22"/>
-      <c r="D48" s="22"/>
-      <c r="E48" s="22"/>
-      <c r="F48" s="31" t="n">
-        <f aca="false">COUNTA(D13:D15)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="22" t="s">
-        <v>335</v>
-      </c>
-      <c r="C49" s="22"/>
-      <c r="D49" s="22"/>
-      <c r="E49" s="22"/>
-      <c r="F49" s="31" t="n">
-        <f aca="false">COUNTA(D16:D18)</f>
-        <v>3</v>
-      </c>
+      <c r="C49" s="21"/>
+      <c r="D49" s="21"/>
+      <c r="E49" s="21"/>
+      <c r="F49" s="21"/>
+      <c r="G49" s="21"/>
+      <c r="H49" s="21"/>
     </row>
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="22" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C50" s="22"/>
       <c r="D50" s="22"/>
       <c r="E50" s="22"/>
       <c r="F50" s="31" t="n">
-        <f aca="false">COUNTA(D19:D21)</f>
-        <v>3</v>
+        <f aca="false">COUNTA(D13:D17)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="22" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C51" s="22"/>
       <c r="D51" s="22"/>
       <c r="E51" s="22"/>
       <c r="F51" s="31" t="n">
-        <f aca="false">COUNTA(D22:D24)</f>
+        <f aca="false">COUNTA(D18:D20)</f>
         <v>3</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="22" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C52" s="22"/>
       <c r="D52" s="22"/>
       <c r="E52" s="22"/>
       <c r="F52" s="31" t="n">
-        <f aca="false">COUNTA(D25:D27)</f>
+        <f aca="false">COUNTA(D21:D23)</f>
         <v>3</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="22" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C53" s="22"/>
       <c r="D53" s="22"/>
       <c r="E53" s="22"/>
       <c r="F53" s="31" t="n">
-        <f aca="false">COUNTA(D28:D31)</f>
-        <v>4</v>
+        <f aca="false">COUNTA(D24:D26)</f>
+        <v>3</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="22" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C54" s="22"/>
       <c r="D54" s="22"/>
       <c r="E54" s="22"/>
       <c r="F54" s="31" t="n">
-        <f aca="false">COUNTA(D32:D34)</f>
+        <f aca="false">COUNTA(D27:D29)</f>
         <v>3</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="22" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C55" s="22"/>
       <c r="D55" s="22"/>
       <c r="E55" s="22"/>
       <c r="F55" s="31" t="n">
-        <f aca="false">COUNTIF(B38:B45,"Recebe de")</f>
-        <v>5</v>
+        <f aca="false">COUNTA(D30:D33)</f>
+        <v>4</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="22" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C56" s="22"/>
       <c r="D56" s="22"/>
       <c r="E56" s="22"/>
       <c r="F56" s="31" t="n">
-        <f aca="false">COUNTIF(B38:B45,"Entrega a")</f>
+        <f aca="false">COUNTA(D34:D36)</f>
         <v>3</v>
       </c>
     </row>
+    <row r="57" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B57" s="22" t="s">
+        <v>342</v>
+      </c>
+      <c r="C57" s="22"/>
+      <c r="D57" s="22"/>
+      <c r="E57" s="22"/>
+      <c r="F57" s="31" t="n">
+        <f aca="false">COUNTIF(B40:B47,"Recebe de")</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B58" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="C58" s="22"/>
+      <c r="D58" s="22"/>
+      <c r="E58" s="22"/>
+      <c r="F58" s="31" t="n">
+        <f aca="false">COUNTIF(B40:B47,"Entrega a")</f>
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="122">
+  <mergeCells count="128">
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B4:C4"/>
@@ -8004,13 +8037,13 @@
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="D34:F34"/>
     <mergeCell ref="G34:H34"/>
-    <mergeCell ref="B36:H36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="B38:H38"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="D39:F39"/>
     <mergeCell ref="G39:H39"/>
@@ -8032,9 +8065,13 @@
     <mergeCell ref="B45:C45"/>
     <mergeCell ref="D45:F45"/>
     <mergeCell ref="G45:H45"/>
-    <mergeCell ref="B47:H47"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="B49:H49"/>
     <mergeCell ref="B50:E50"/>
     <mergeCell ref="B51:E51"/>
     <mergeCell ref="B52:E52"/>
@@ -8042,6 +8079,8 @@
     <mergeCell ref="B54:E54"/>
     <mergeCell ref="B55:E55"/>
     <mergeCell ref="B56:E56"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="B58:E58"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
@@ -8051,7 +8090,7 @@
     <oddFooter/>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="35" man="true" max="16383" min="0"/>
+    <brk id="37" man="true" max="16383" min="0"/>
   </rowBreaks>
 </worksheet>
 </file>
--- a/Processos/Processos-modelo.xlsx
+++ b/Processos/Processos-modelo.xlsx
@@ -2016,11 +2016,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="87258834"/>
-        <c:axId val="53690365"/>
+        <c:axId val="42314841"/>
+        <c:axId val="30578834"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="87258834"/>
+        <c:axId val="42314841"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2052,7 +2052,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="53690365"/>
+        <c:crossAx val="30578834"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2060,7 +2060,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="53690365"/>
+        <c:axId val="30578834"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -2101,7 +2101,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="87258834"/>
+        <c:crossAx val="42314841"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="0.25"/>
@@ -2267,11 +2267,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="339729"/>
-        <c:axId val="40387945"/>
+        <c:axId val="47195182"/>
+        <c:axId val="7637829"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="339729"/>
+        <c:axId val="47195182"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2303,7 +2303,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40387945"/>
+        <c:crossAx val="7637829"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2311,7 +2311,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="40387945"/>
+        <c:axId val="7637829"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -2352,7 +2352,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="339729"/>
+        <c:crossAx val="47195182"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="0.25"/>
@@ -4656,13 +4656,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
+    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H4" type="date">
+      <formula1>36526</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" error="Digite um número inteiro de 1 a 12." errorStyle="stop" errorTitle="Número inválido" operator="between" prompt="Número do processo, como na aba Processos." promptTitle="Número" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="D4" type="whole">
       <formula1>1</formula1>
       <formula2>12</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H4" type="date">
-      <formula1>36526</formula1>
-      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
@@ -5967,7 +5967,7 @@
         <v>160</v>
       </c>
       <c r="J11" s="40" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K11" s="40" t="s">
         <v>159</v>
@@ -5979,7 +5979,7 @@
         <v>160</v>
       </c>
       <c r="N11" s="40" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O11" s="40" t="s">
         <v>160</v>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="J20" s="35" t="n">
         <f aca="false">(COUNTIF(J11:J19,"Sim")+0.5*COUNTIF(J11:J19,"Parcial"))/ROWS(J11:J19)</f>
-        <v>0.388888888888889</v>
+        <v>0.444444444444444</v>
       </c>
       <c r="K20" s="35" t="n">
         <f aca="false">(COUNTIF(K11:K19,"Sim")+0.5*COUNTIF(K11:K19,"Parcial"))/ROWS(K11:K19)</f>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="N20" s="35" t="n">
         <f aca="false">(COUNTIF(N11:N19,"Sim")+0.5*COUNTIF(N11:N19,"Parcial"))/ROWS(N11:N19)</f>
-        <v>0.388888888888889</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="O20" s="35" t="n">
         <f aca="false">(COUNTIF(O11:O19,"Sim")+0.5*COUNTIF(O11:O19,"Parcial"))/ROWS(O11:O19)</f>
@@ -6551,7 +6551,7 @@
       <c r="D28" s="22"/>
       <c r="E28" s="23" t="str">
         <f aca="false">INDEX(H10:O10,MATCH(MIN(H20:O20),H20:O20,0))</f>
-        <v>c · Critérios e indicadores</v>
+        <v>g · Avaliação e mudanças</v>
       </c>
       <c r="F28" s="23"/>
       <c r="G28" s="23"/>
